--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA98BCD-96A5-9149-9C0E-177DCE9BCC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF124AD-9046-AF41-8B26-C6F2E17B409D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="2560" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
   <si>
     <t>Date</t>
   </si>
@@ -227,6 +227,15 @@
   </si>
   <si>
     <t>No Meetup - Thanksgiving</t>
+  </si>
+  <si>
+    <t>7:00 pm</t>
+  </si>
+  <si>
+    <t>MSDS and MSGenAI Orientation</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OTHZTFeBsJE</t>
   </si>
 </sst>
 </file>
@@ -621,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA12B6D5-EAC3-1C40-AC8A-3C6A227098E4}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
@@ -662,82 +671,79 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="H2" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>46272</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <f>A3+7</f>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <f>A4+7</f>
         <v>46279</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
         <v>59</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>42</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <f t="shared" ref="A5:A17" si="0">A4+7</f>
-        <v>46286</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
       </c>
       <c r="F5" s="8"/>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <f t="shared" si="0"/>
-        <v>46293</v>
+        <f t="shared" ref="A6:A18" si="0">A5+7</f>
+        <v>46286</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>7</v>
@@ -746,17 +752,18 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>7</v>
@@ -765,46 +772,46 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>46307</v>
+        <v>46300</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="6"/>
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>46314</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
+        <v>46307</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>7</v>
@@ -813,17 +820,17 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>7</v>
@@ -832,17 +839,17 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>7</v>
@@ -851,17 +858,17 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>7</v>
@@ -870,46 +877,46 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>46349</v>
+        <v>46342</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" s="8"/>
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>46356</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>8</v>
+        <v>46349</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="H15" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>7</v>
@@ -918,37 +925,56 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="6"/>
+        <v>49</v>
+      </c>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
+        <v>46363</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
         <v>46370</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="B18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H20" s="5"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H21" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF124AD-9046-AF41-8B26-C6F2E17B409D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABD8D9B-CE27-AE4F-8CD7-CFC011DB0348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="2560" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="1560" yWindow="10560" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
   <si>
     <t>Date</t>
   </si>
@@ -235,7 +235,13 @@
     <t>MSDS and MSGenAI Orientation</t>
   </si>
   <si>
-    <t>https://youtu.be/OTHZTFeBsJE</t>
+    <t>bdOZOmdE2Nw</t>
+  </si>
+  <si>
+    <t>00-Intro_to_Course</t>
+  </si>
+  <si>
+    <t>Ns_PDkB3UBE</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,12 @@
       <c r="D3" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="10"/>
+      <c r="F3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" t="s">
+        <v>67</v>
+      </c>
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Dropbox/SPS Dropbox/Jason Bryer/Teaching/DATA606 2026 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABD8D9B-CE27-AE4F-8CD7-CFC011DB0348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB506D9F-BCD8-2D4B-8C3C-C296C919B440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="10560" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -242,6 +242,12 @@
   </si>
   <si>
     <t>Ns_PDkB3UBE</t>
+  </si>
+  <si>
+    <t>01-Intro_to_Data</t>
+  </si>
+  <si>
+    <t>IsR5Ed7uivE</t>
   </si>
 </sst>
 </file>
@@ -729,6 +735,12 @@
       <c r="E4" t="s">
         <v>41</v>
       </c>
+      <c r="F4" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" t="s">
+        <v>69</v>
+      </c>
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
